--- a/estimate_scenarios.xlsx
+++ b/estimate_scenarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v-minasyanva\Downloads\MS Architecture Center Scanner and Estimate Comparison Tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v-minasyanva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0016D6D2-FF5A-45F8-8AD1-A89AF123FE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320E8621-AE04-4E03-966E-CFA3DCFFEB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33720" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{8CC6B35D-15F8-46B2-8EDB-45E5A707818B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
   <si>
     <t>status</t>
   </si>
@@ -158,15 +158,9 @@
     <t>https://azure.com/e/375d2b930db14fbe90537421331f41de</t>
   </si>
   <si>
-    <t>https://azure.com/e/c42b93df96a64d9d9067d2cbc1c0c4d2</t>
-  </si>
-  <si>
     <t>https://azure.com/e/6f9f52a0c7be4cbd9ae8bd8b77200396</t>
   </si>
   <si>
-    <t>https://azure.com/e/82efdb5321cc4c58aafa84607f68c24a</t>
-  </si>
-  <si>
     <t>https://azure.com/e/c0979505ef6a45409c218c24ee4033de</t>
   </si>
   <si>
@@ -200,9 +194,6 @@
     <t>https://azure.com/e/625cea91d4aa43bca73e0a8235817ba7</t>
   </si>
   <si>
-    <t>https://azure.com/e/ed90eb013b60448684b3ef40d123ff13</t>
-  </si>
-  <si>
     <t>https://azure.com/e/e0b74472f72d48ce891b08b3af105872</t>
   </si>
   <si>
@@ -218,9 +209,6 @@
     <t>https://azure.com/e/2554c32b19c24b3d9f90d2a73683bd6a</t>
   </si>
   <si>
-    <t>https://azure.com/e/998db680fa18493496b71277c08322e7</t>
-  </si>
-  <si>
     <t>https://azure.microsoft.com/pricing/calculator/?service=kubernetes-service</t>
   </si>
   <si>
@@ -236,9 +224,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>This is just for reference. This scenario is already included in calculator using baseline-microsoft-foundry-chat article</t>
-  </si>
-  <si>
     <t>https://learn.microsoft.com/en-us/azure/architecture/web-apps/guides/networking/access-multitenant-web-app-from-on-premises</t>
   </si>
   <si>
@@ -248,13 +233,43 @@
     <t>https://azure.microsoft.com/pricing/calculator/?shared-estimate=61029210b61b4cce8602cb905d7c0dda</t>
   </si>
   <si>
-    <t>Need to update the estimate link in the Calculator</t>
-  </si>
-  <si>
-    <t>Scanner needs to be update to show this as match. Small deployment estimate is being used for Pricing calculator</t>
-  </si>
-  <si>
-    <t>This article doesn't inlcude the saved estimate link but it was manually provided to us to include in the calculator. Vahe reached out to the team asking to update the article to include the saved estimate link there as well.</t>
+    <t>Update submitted on 3/2</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/b7574e1a2952486e94073601a26ad52f</t>
+  </si>
+  <si>
+    <t>New estimate link</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/b00c1854756f4687a4fcbe0916951aba</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/e9fb45165e1c4ef0b46d880d818355cb</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/16fc0fecb81e49ddadc91f2a0d0ecffc</t>
+  </si>
+  <si>
+    <t>Submitted on 3/2</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/reference-architectures/containers/aks-multi-region/aks-multi-cluster</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/2e3a4a64be264e8781f719bbd194e904</t>
+  </si>
+  <si>
+    <t>New scenario with an estimate</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/web-apps/app-service/architectures/baseline-zone-redundant</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/04fa6a287c1d47f9af40c91e4202f238</t>
+  </si>
+  <si>
+    <t>For reference only. This scenario is included in calculator under "Basic Microsoft Foundry Chat"</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1F846C-8C34-46B3-86FF-223EECDE71CC}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.6328125" customWidth="1"/>
@@ -1136,102 +1151,102 @@
         <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -1239,10 +1254,10 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -1250,7 +1265,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
@@ -1261,7 +1276,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
         <v>43</v>
@@ -1269,10 +1284,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
         <v>44</v>
@@ -1283,10 +1298,10 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -1294,10 +1309,10 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -1305,10 +1320,10 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -1316,186 +1331,211 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>2</v>
       </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>2</v>
-      </c>
-      <c r="B25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>32</v>
-      </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>2</v>
       </c>
       <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
         <v>12</v>
       </c>
-      <c r="C29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" t="s">
-        <v>64</v>
+      <c r="C34" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
